--- a/grupos/6APV - Estadisticos 20232.xlsx
+++ b/grupos/6APV - Estadisticos 20232.xlsx
@@ -137,10 +137,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
+    <t>Rodríguez Román Leticia</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
@@ -149,9 +152,6 @@
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
@@ -167,22 +167,22 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>JOSE ANTONIO</t>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
   </si>
 </sst>
 </file>
@@ -690,22 +690,22 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -726,13 +726,13 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -767,22 +767,22 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -806,7 +806,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -844,22 +844,22 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -880,16 +880,16 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>8</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -921,22 +921,22 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -957,7 +957,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -969,10 +969,10 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -998,22 +998,22 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1034,13 +1034,13 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>10</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1075,22 +1075,22 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1111,10 +1111,10 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1123,7 +1123,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1152,22 +1152,22 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1188,19 +1188,19 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>9</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1229,22 +1229,22 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1277,10 +1277,10 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1306,22 +1306,22 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1345,19 +1345,19 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1383,22 +1383,22 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1460,22 +1460,22 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1537,22 +1537,22 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1576,19 +1576,19 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>7</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1614,22 +1614,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1650,13 +1650,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1665,7 +1665,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1691,22 +1691,22 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1727,7 +1727,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -1739,7 +1739,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -1768,22 +1768,22 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1807,10 +1807,10 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -1955,7 +1955,7 @@
         <v>96</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -1970,10 +1970,10 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -1988,7 +1988,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2014,40 +2014,40 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>96.7</v>
+        <v>90</v>
       </c>
       <c r="I5">
         <v>100</v>
       </c>
       <c r="J5">
-        <v>88</v>
+        <v>72.5</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N5">
-        <v>96.7</v>
+        <v>90</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>88</v>
+        <v>72.5</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2073,40 +2073,40 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="I6">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J6">
-        <v>68</v>
+        <v>47.1</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="N6">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="O6">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P6">
-        <v>68</v>
+        <v>47.1</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2132,13 +2132,13 @@
         <v>88</v>
       </c>
       <c r="H7">
-        <v>83.3</v>
+        <v>90</v>
       </c>
       <c r="I7">
         <v>100</v>
       </c>
       <c r="J7">
-        <v>80</v>
+        <v>86.3</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -2147,16 +2147,16 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N7">
-        <v>83.3</v>
+        <v>90</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
-        <v>80</v>
+        <v>86.3</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -2165,7 +2165,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2191,10 +2191,10 @@
         <v>96</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I8">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -2206,13 +2206,13 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O8">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -2224,7 +2224,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2262,7 +2262,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -2280,7 +2280,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -2309,40 +2309,40 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="I10">
         <v>100</v>
       </c>
       <c r="J10">
-        <v>88</v>
+        <v>76.5</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N10">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>88</v>
+        <v>76.5</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2427,40 +2427,40 @@
         <v>92</v>
       </c>
       <c r="H12">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="I12">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J12">
-        <v>84</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="M12">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N12">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="O12">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="P12">
-        <v>84</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="S12">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2489,16 +2489,16 @@
         <v>93.3</v>
       </c>
       <c r="I13">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -2507,16 +2507,16 @@
         <v>93.3</v>
       </c>
       <c r="O13">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -2545,37 +2545,37 @@
         <v>60</v>
       </c>
       <c r="H14">
-        <v>56.7</v>
+        <v>28.3</v>
       </c>
       <c r="I14">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J14">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="K14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L14">
-        <v>80</v>
+        <v>43.6</v>
       </c>
       <c r="M14">
         <v>60</v>
       </c>
       <c r="N14">
-        <v>56.7</v>
+        <v>28.3</v>
       </c>
       <c r="O14">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="P14">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="Q14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="R14">
-        <v>80</v>
+        <v>43.6</v>
       </c>
       <c r="S14">
         <v>60</v>
@@ -2604,40 +2604,40 @@
         <v>88</v>
       </c>
       <c r="H15">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="I15">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J15">
+        <v>76.5</v>
+      </c>
+      <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
+        <v>92.7</v>
+      </c>
+      <c r="M15">
         <v>84</v>
       </c>
-      <c r="K15">
-        <v>100</v>
-      </c>
-      <c r="L15">
-        <v>93.3</v>
-      </c>
-      <c r="M15">
-        <v>88</v>
-      </c>
       <c r="N15">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="O15">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P15">
+        <v>76.5</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
+        <v>92.7</v>
+      </c>
+      <c r="S15">
         <v>84</v>
-      </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
-      <c r="R15">
-        <v>93.3</v>
-      </c>
-      <c r="S15">
-        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2663,13 +2663,13 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="I16">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J16">
-        <v>84</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -2681,13 +2681,13 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="O16">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P16">
-        <v>84</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -2722,40 +2722,40 @@
         <v>92</v>
       </c>
       <c r="H17">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
+        <v>84.3</v>
+      </c>
+      <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
+        <v>98.2</v>
+      </c>
+      <c r="M17">
         <v>96</v>
       </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
-      <c r="L17">
-        <v>96.7</v>
-      </c>
-      <c r="M17">
-        <v>92</v>
-      </c>
       <c r="N17">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
+        <v>84.3</v>
+      </c>
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
+        <v>98.2</v>
+      </c>
+      <c r="S17">
         <v>96</v>
-      </c>
-      <c r="Q17">
-        <v>100</v>
-      </c>
-      <c r="R17">
-        <v>96.7</v>
-      </c>
-      <c r="S17">
-        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -2787,7 +2787,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>84</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -2805,7 +2805,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>84</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -2871,7 +2871,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>39</v>
@@ -2880,19 +2880,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>80</v>
+        <v>73.3</v>
       </c>
       <c r="G2" s="2">
-        <v>20</v>
+        <v>26.7</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2903,7 +2903,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>40</v>
@@ -2912,19 +2912,19 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>86.7</v>
+        <v>80</v>
       </c>
       <c r="G3" s="2">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>41</v>
@@ -2944,19 +2944,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="G4" s="2">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>42</v>
@@ -2988,7 +2988,7 @@
         <v>6.7</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
@@ -3020,7 +3020,7 @@
         <v>6.7</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3052,7 +3052,7 @@
         <v>6.7</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920314</v>
+        <v>21330051920125</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -3149,7 +3149,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920314</v>
+        <v>21330051920125</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -3172,7 +3172,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920125</v>
+        <v>21330051920122</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -3192,7 +3192,7 @@
         <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>

--- a/grupos/6APV - Estadisticos 20232.xlsx
+++ b/grupos/6APV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="52">
   <si>
     <t>Materia</t>
   </si>
@@ -137,24 +137,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -167,22 +167,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -708,22 +699,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -732,7 +723,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -785,25 +776,25 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -812,7 +803,7 @@
         <v>6</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -862,22 +853,22 @@
         <v>4</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -892,10 +883,10 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -939,22 +930,22 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -966,10 +957,10 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1016,22 +1007,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1040,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1093,22 +1084,22 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1117,13 +1108,13 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>8</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1170,22 +1161,22 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1197,7 +1188,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1247,22 +1238,22 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1324,25 +1315,25 @@
         <v>4</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1357,7 +1348,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1401,22 +1392,22 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1431,7 +1422,7 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1478,22 +1469,22 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>5</v>
@@ -1555,40 +1546,40 @@
         <v>4</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>8</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1632,22 +1623,22 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1659,7 +1650,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -1709,22 +1700,22 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -1733,13 +1724,13 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>7</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -1786,22 +1777,22 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -1813,13 +1804,13 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1973,7 +1964,7 @@
         <v>98</v>
       </c>
       <c r="N4">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -1988,7 +1979,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>98</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2032,22 +2023,22 @@
         <v>96</v>
       </c>
       <c r="N5">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>72.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="S5">
-        <v>96</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2079,7 +2070,7 @@
         <v>98.3</v>
       </c>
       <c r="J6">
-        <v>47.1</v>
+        <v>92.2</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -2091,22 +2082,22 @@
         <v>86</v>
       </c>
       <c r="N6">
-        <v>80</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="O6">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P6">
-        <v>47.1</v>
+        <v>90.8</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S6">
-        <v>86</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2150,13 +2141,13 @@
         <v>90</v>
       </c>
       <c r="N7">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
-        <v>86.3</v>
+        <v>86.8</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -2165,7 +2156,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2209,10 +2200,10 @@
         <v>98</v>
       </c>
       <c r="N8">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="O8">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -2224,7 +2215,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>98</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2280,7 +2271,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -2327,22 +2318,22 @@
         <v>94</v>
       </c>
       <c r="N10">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>76.5</v>
+        <v>84.2</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="S10">
-        <v>94</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2392,7 +2383,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -2445,22 +2436,22 @@
         <v>88</v>
       </c>
       <c r="N12">
-        <v>86.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="O12">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="P12">
-        <v>82.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="S12">
-        <v>88</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2504,10 +2495,10 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="O13">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P13">
         <v>88.2</v>
@@ -2516,7 +2507,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -2563,22 +2554,22 @@
         <v>60</v>
       </c>
       <c r="N14">
-        <v>28.3</v>
+        <v>17.7</v>
       </c>
       <c r="O14">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="P14">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="Q14">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="R14">
-        <v>43.6</v>
+        <v>30</v>
       </c>
       <c r="S14">
-        <v>60</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2622,22 +2613,22 @@
         <v>84</v>
       </c>
       <c r="N15">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="O15">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P15">
-        <v>76.5</v>
+        <v>84.2</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>92.7</v>
+        <v>95</v>
       </c>
       <c r="S15">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2681,13 +2672,13 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O16">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P16">
-        <v>96.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -2740,22 +2731,22 @@
         <v>96</v>
       </c>
       <c r="N17">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>84.3</v>
+        <v>89.5</v>
       </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="S17">
-        <v>96</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -2805,7 +2796,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>96.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -2871,7 +2862,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>39</v>
@@ -2880,19 +2871,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>73.3</v>
+        <v>86.7</v>
       </c>
       <c r="G2" s="2">
-        <v>26.7</v>
+        <v>13.3</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2903,7 +2894,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>40</v>
@@ -2912,19 +2903,19 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>80</v>
+        <v>93.3</v>
       </c>
       <c r="G3" s="2">
-        <v>20</v>
+        <v>6.7</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2935,7 +2926,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>41</v>
@@ -2944,19 +2935,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="G4" s="2">
-        <v>13.3</v>
+        <v>6.7</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2967,7 +2958,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>42</v>
@@ -2988,7 +2979,7 @@
         <v>6.7</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2999,7 +2990,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
@@ -3020,7 +3011,7 @@
         <v>6.7</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3031,7 +3022,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
@@ -3052,7 +3043,7 @@
         <v>6.7</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3102,7 +3093,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3134,70 +3125,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920125</v>
+        <v>19330051920314</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
       </c>
       <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" t="s">
-        <v>53</v>
-      </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920125</v>
-      </c>
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920122</v>
-      </c>
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
     </row>
